--- a/master/result/97_穿越时空_遇见你/97_穿越时空_遇见你.xlsx
+++ b/master/result/97_穿越时空_遇见你/97_穿越时空_遇见你.xlsx
@@ -397,368 +397,465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:D32"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>tonight</v>
       </c>
       <c r="B2" t="str">
-        <v>tonight</v>
+        <v>/tonight/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>今晚</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>page</v>
       </c>
       <c r="B3" t="str">
-        <v>page</v>
+        <v>/page/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>页</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>quite</v>
       </c>
       <c r="B4" t="str">
-        <v>quite</v>
+        <v>/quite/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>相当</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>stadium</v>
       </c>
       <c r="B5" t="str">
-        <v>stadium</v>
+        <v>/stadium/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>体育场</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>floor</v>
       </c>
       <c r="B6" t="str">
-        <v>floor</v>
+        <v>/floor/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>楼层</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>projector</v>
       </c>
       <c r="B7" t="str">
-        <v>projector</v>
+        <v>/projector/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>投影仪</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>wander</v>
       </c>
       <c r="B8" t="str">
-        <v>wander</v>
+        <v>/wander/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>漫步</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>tennis</v>
       </c>
       <c r="B9" t="str">
-        <v>tennis</v>
+        <v>/tennis/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>网球</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>strong</v>
       </c>
       <c r="B10" t="str">
-        <v>strong</v>
+        <v>/strong/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>强烈的</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>print</v>
       </c>
       <c r="B11" t="str">
-        <v>print</v>
+        <v>/prɪnt/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>印刷</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>eastern</v>
       </c>
       <c r="B12" t="str">
-        <v>eastern</v>
+        <v>/eastern/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>东方的</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>do</v>
       </c>
       <c r="B13" t="str">
-        <v>do</v>
+        <v>/duː/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>做</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>reveal</v>
       </c>
       <c r="B14" t="str">
-        <v>reveal</v>
+        <v>/rɪˈviːl/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>显示</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>nerve</v>
       </c>
       <c r="B15" t="str">
-        <v>nerve</v>
+        <v>/nerve/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>勇气</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>bulk</v>
       </c>
       <c r="B16" t="str">
-        <v>bulk</v>
+        <v>/bulk/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>大量</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>increase</v>
       </c>
       <c r="B17" t="str">
-        <v>increase</v>
+        <v>/ɪnˈkriːs/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>增加</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>spicy</v>
       </c>
       <c r="B18" t="str">
-        <v>spicy</v>
+        <v>/spicy/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>浓郁的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>diverse</v>
       </c>
       <c r="B19" t="str">
-        <v>diverse</v>
+        <v>/diverse/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>不同的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>meal</v>
       </c>
       <c r="B20" t="str">
-        <v>meal</v>
+        <v>/meal/</v>
       </c>
       <c r="C20" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>餐</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>deadline</v>
       </c>
       <c r="B21" t="str">
-        <v>deadline</v>
+        <v>/deadline/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>最后期限</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>chemical</v>
       </c>
       <c r="B22" t="str">
-        <v>chemical</v>
+        <v>/ˈkemɪkəl/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>化学</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>declare</v>
       </c>
       <c r="B23" t="str">
-        <v>declare</v>
+        <v>/dɪˈkleə/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>宣布</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>chance</v>
       </c>
       <c r="B24" t="str">
-        <v>chance</v>
+        <v>/chance/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>机会</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>enterprise</v>
       </c>
       <c r="B25" t="str">
-        <v>enterprise</v>
+        <v>/enterprise/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>进取心</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>military</v>
       </c>
       <c r="B26" t="str">
-        <v>military</v>
+        <v>/military/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>军事</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>wealth</v>
       </c>
       <c r="B27" t="str">
-        <v>wealth</v>
+        <v>/wealth/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>财富</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>march</v>
       </c>
       <c r="B28" t="str">
-        <v>march</v>
+        <v>/mɑːtʃ/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>行进</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>isle</v>
       </c>
       <c r="B29" t="str">
-        <v>isle</v>
+        <v>/isle/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>小岛</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>fly</v>
       </c>
       <c r="B30" t="str">
-        <v>fly</v>
+        <v>/flaɪ/</v>
       </c>
       <c r="C30" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D30" t="str">
         <v>飞</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>thus</v>
       </c>
       <c r="B31" t="str">
-        <v>thus</v>
+        <v>/thus/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>如此</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>wild</v>
       </c>
       <c r="B32" t="str">
-        <v>wild</v>
+        <v>/wild/</v>
       </c>
       <c r="C32" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>狂野的</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>